--- a/AVGO.xlsx
+++ b/AVGO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CC33E8C-3DCA-43CF-86B3-E3D682734F95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0F6C593-E98D-4E5A-9EE0-95BED5F1D5CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="50490" yWindow="680" windowWidth="24340" windowHeight="15680" xr2:uid="{70329CC5-8756-4BA4-A5C1-E709DAADAB52}"/>
+    <workbookView xWindow="-210" yWindow="4790" windowWidth="23600" windowHeight="13830" xr2:uid="{70329CC5-8756-4BA4-A5C1-E709DAADAB52}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -36,8 +36,26 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={679F8F37-EAFB-4A83-A0B8-82580466F48F}</author>
+  </authors>
+  <commentList>
+    <comment ref="P10" authorId="0" shapeId="0" xr:uid="{679F8F37-EAFB-4A83-A0B8-82580466F48F}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    19.1m guidance Q425 call</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="101">
   <si>
     <t>Price</t>
   </si>
@@ -225,9 +243,6 @@
     <t>FC SAN (fibre channel)</t>
   </si>
   <si>
-    <t>hybrid cloud</t>
-  </si>
-  <si>
     <t>11/22/23: VMware deal closes: $86.3B.</t>
   </si>
   <si>
@@ -303,7 +318,46 @@
     <t>Net Cash</t>
   </si>
   <si>
-    <t>Q325</t>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>FQ126</t>
+  </si>
+  <si>
+    <t>FQ226</t>
+  </si>
+  <si>
+    <t>FQ326</t>
+  </si>
+  <si>
+    <t>FQ426</t>
+  </si>
+  <si>
+    <t>Customers</t>
+  </si>
+  <si>
+    <t>AAPL</t>
+  </si>
+  <si>
+    <t>GOOGL</t>
+  </si>
+  <si>
+    <t>META</t>
+  </si>
+  <si>
+    <t>MSFT</t>
+  </si>
+  <si>
+    <t>AMZN</t>
+  </si>
+  <si>
+    <t>OpenAI</t>
+  </si>
+  <si>
+    <t>11/22/23 acquisition $84B</t>
+  </si>
+  <si>
+    <t>AI Revenue</t>
   </si>
 </sst>
 </file>
@@ -313,7 +367,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yy;@"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -332,6 +386,20 @@
       <sz val="10"/>
       <color theme="10"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -356,7 +424,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -388,6 +456,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -412,16 +481,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>44431</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>32524</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>11906</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>44431</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>137358</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>32524</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>125452</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -436,7 +505,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8616931" y="11906"/>
+          <a:off x="9763899" y="0"/>
           <a:ext cx="0" cy="11103015"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -462,15 +531,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>22</xdr:col>
+      <xdr:col>26</xdr:col>
       <xdr:colOff>32523</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
+      <xdr:col>26</xdr:col>
       <xdr:colOff>32523</xdr:colOff>
-      <xdr:row>69</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>125452</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -511,6 +580,12 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Martin Shkreli" id="{436DC3BB-F43E-4E5A-A506-DB6F21C9D457}" userId="9ffda80931a57275" providerId="Windows Live"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -828,9 +903,17 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="P10" dT="2026-03-29T12:55:11.04" personId="{436DC3BB-F43E-4E5A-A506-DB6F21C9D457}" id="{679F8F37-EAFB-4A83-A0B8-82580466F48F}">
+    <text>19.1m guidance Q425 call</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9849E712-1B47-42A3-A902-777D3000824F}">
-  <dimension ref="B2:K17"/>
+  <dimension ref="B2:K26"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="2:11" x14ac:dyDescent="0.25">
@@ -838,7 +921,7 @@
         <v>0</v>
       </c>
       <c r="J2" s="1">
-        <v>376</v>
+        <v>315</v>
       </c>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.25">
@@ -849,10 +932,10 @@
         <v>1</v>
       </c>
       <c r="J3" s="2">
-        <v>4860</v>
+        <v>4888</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="2:11" ht="13" x14ac:dyDescent="0.3">
@@ -864,7 +947,7 @@
       </c>
       <c r="J4" s="5">
         <f>+J2*J3</f>
-        <v>1827360</v>
+        <v>1539720</v>
       </c>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.25">
@@ -875,10 +958,10 @@
         <v>3</v>
       </c>
       <c r="J5" s="2">
-        <v>10718</v>
+        <v>14174</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.25">
@@ -889,10 +972,10 @@
         <v>4</v>
       </c>
       <c r="J6" s="2">
-        <v>64229</v>
+        <v>66057</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.25">
@@ -904,7 +987,7 @@
       </c>
       <c r="J7" s="2">
         <f>+J4-J5+J6</f>
-        <v>1880871</v>
+        <v>1591603</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.25">
@@ -917,7 +1000,7 @@
         <v>58</v>
       </c>
       <c r="C9" t="s">
-        <v>62</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.25">
@@ -927,7 +1010,7 @@
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.25">
@@ -940,22 +1023,57 @@
         <v>61</v>
       </c>
       <c r="I14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.25">
       <c r="I15" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>76</v>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" ht="13" x14ac:dyDescent="0.3">
+      <c r="C20" s="15" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C21" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C22" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C23" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C24" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C25" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C26" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -964,26 +1082,26 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{470E0775-30FD-4D74-BE40-C6F63DB74CF0}">
-  <dimension ref="A1:X71"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{470E0775-30FD-4D74-BE40-C6F63DB74CF0}">
+  <dimension ref="A1:AB72"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="15" width="8.26953125" style="3" customWidth="1"/>
-    <col min="16" max="16" width="9.1796875" style="3"/>
-    <col min="17" max="19" width="8.7265625" style="3"/>
+    <col min="3" max="19" width="8.26953125" style="3" customWidth="1"/>
     <col min="20" max="20" width="9.1796875" style="3"/>
-    <col min="21" max="22" width="10.26953125" style="3" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="9.1796875" style="3"/>
+    <col min="21" max="23" width="8.7265625" style="3"/>
+    <col min="24" max="24" width="9.1796875" style="3"/>
+    <col min="25" max="26" width="10.26953125" style="3" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="9.1796875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="C2" s="3" t="s">
         <v>51</v>
       </c>
@@ -1006,46 +1124,58 @@
         <v>8</v>
       </c>
       <c r="J2" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="L2" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="M2" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="N2" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="O2" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="O2" s="3" t="s">
-        <v>82</v>
+      <c r="P2" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>89</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="S2" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="V2" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="T2" s="3" t="s">
+      <c r="W2" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="X2" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y2" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="U2" s="3" t="s">
+      <c r="Z2" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="V2" s="3" t="s">
+      <c r="AA2" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="W2" s="3" t="s">
+      <c r="AB2" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="X2" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:28" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B3" s="13" t="s">
         <v>19</v>
       </c>
@@ -1091,21 +1221,40 @@
         <f>+K3+365</f>
         <v>45958</v>
       </c>
-      <c r="P3" s="14"/>
-      <c r="Q3" s="14"/>
-      <c r="R3" s="14"/>
-      <c r="S3" s="14"/>
+      <c r="P3" s="14">
+        <f>+L3+365</f>
+        <v>46056</v>
+      </c>
+      <c r="Q3" s="14">
+        <f>+M3+365</f>
+        <v>46146</v>
+      </c>
+      <c r="R3" s="14">
+        <f>+N3+365</f>
+        <v>46237</v>
+      </c>
+      <c r="S3" s="14">
+        <f>+O3+365</f>
+        <v>46323</v>
+      </c>
       <c r="T3" s="14"/>
-      <c r="U3" s="14">
-        <v>44864</v>
-      </c>
-      <c r="V3" s="14">
-        <v>45228</v>
-      </c>
+      <c r="U3" s="14"/>
+      <c r="V3" s="14"/>
       <c r="W3" s="14"/>
       <c r="X3" s="14"/>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y3" s="14">
+        <v>44864</v>
+      </c>
+      <c r="Z3" s="14">
+        <v>45228</v>
+      </c>
+      <c r="AA3" s="14"/>
+      <c r="AB3" s="14"/>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>100</v>
+      </c>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
@@ -1113,87 +1262,108 @@
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
       <c r="I4" s="7"/>
-      <c r="U4" s="7"/>
-      <c r="V4" s="7"/>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>83</v>
-      </c>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="8"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="8">
+        <v>8400</v>
+      </c>
+      <c r="Q4" s="8">
+        <v>10700</v>
+      </c>
+      <c r="Y4" s="7"/>
+      <c r="Z4" s="7"/>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
-      <c r="F5" s="8">
-        <v>6941</v>
-      </c>
+      <c r="F5" s="7"/>
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
       <c r="I5" s="7"/>
-      <c r="J5" s="8">
-        <v>7274</v>
-      </c>
-      <c r="K5" s="8">
-        <f>+J5+100</f>
-        <v>7374</v>
-      </c>
-      <c r="U5" s="7"/>
-      <c r="V5" s="7"/>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="8"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
+      <c r="Y5" s="7"/>
+      <c r="Z5" s="7"/>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
       <c r="F6" s="8">
-        <v>1935</v>
+        <v>6941</v>
       </c>
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
       <c r="J6" s="8">
-        <v>5798</v>
+        <v>7274</v>
       </c>
       <c r="K6" s="8">
         <f>+J6+100</f>
-        <v>5898</v>
-      </c>
-      <c r="U6" s="7"/>
-      <c r="V6" s="7"/>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+        <v>7374</v>
+      </c>
+      <c r="L6" s="8">
+        <v>8212</v>
+      </c>
+      <c r="M6" s="8"/>
+      <c r="N6" s="8"/>
+      <c r="O6" s="8">
+        <v>11072</v>
+      </c>
+      <c r="P6" s="8">
+        <v>12515</v>
+      </c>
+      <c r="Y6" s="7"/>
+      <c r="Z6" s="7"/>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
+      <c r="F7" s="8">
+        <v>1935</v>
+      </c>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
       <c r="I7" s="7"/>
       <c r="J7" s="8">
-        <v>7439</v>
+        <v>5798</v>
       </c>
       <c r="K7" s="8">
-        <f>+J7+500</f>
-        <v>7939</v>
-      </c>
-      <c r="T7" s="8">
-        <v>20886</v>
-      </c>
-      <c r="U7" s="8">
-        <v>26277</v>
-      </c>
-      <c r="V7" s="8">
-        <v>27891</v>
-      </c>
-      <c r="W7" s="8"/>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+        <f>+J7+100</f>
+        <v>5898</v>
+      </c>
+      <c r="L7" s="8">
+        <v>6704</v>
+      </c>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8">
+        <v>6943</v>
+      </c>
+      <c r="P7" s="8">
+        <v>6796</v>
+      </c>
+      <c r="Y7" s="7"/>
+      <c r="Z7" s="7"/>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -1203,1111 +1373,1259 @@
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
       <c r="J8" s="8">
-        <v>5633</v>
+        <v>7439</v>
       </c>
       <c r="K8" s="8">
         <f>+J8+500</f>
+        <v>7939</v>
+      </c>
+      <c r="L8" s="8">
+        <v>10143</v>
+      </c>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8">
+        <v>14130</v>
+      </c>
+      <c r="X8" s="8">
+        <v>20886</v>
+      </c>
+      <c r="Y8" s="8">
+        <v>26277</v>
+      </c>
+      <c r="Z8" s="8">
+        <v>27891</v>
+      </c>
+      <c r="AA8" s="8"/>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="8">
+        <v>5633</v>
+      </c>
+      <c r="K9" s="8">
+        <f>+J9+500</f>
         <v>6133</v>
       </c>
-      <c r="T8" s="8">
+      <c r="L9" s="8">
+        <v>4773</v>
+      </c>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="8"/>
+      <c r="P9" s="8">
+        <v>5181</v>
+      </c>
+      <c r="X9" s="8">
         <v>6564</v>
       </c>
-      <c r="U8" s="8">
+      <c r="Y9" s="8">
         <v>6926</v>
       </c>
-      <c r="V8" s="8">
+      <c r="Z9" s="8">
         <v>7928</v>
       </c>
-      <c r="W8" s="8"/>
-    </row>
-    <row r="9" spans="1:24" s="4" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="B9" s="4" t="s">
+      <c r="AA9" s="8"/>
+    </row>
+    <row r="10" spans="1:28" s="4" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="B10" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C10" s="10">
         <v>8930</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D10" s="10">
         <v>8915</v>
       </c>
-      <c r="E9" s="10">
+      <c r="E10" s="10">
         <v>8733</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F10" s="10">
         <v>8876</v>
       </c>
-      <c r="G9" s="10">
+      <c r="G10" s="10">
         <v>9295</v>
       </c>
-      <c r="H9" s="10">
+      <c r="H10" s="10">
         <v>11961</v>
       </c>
-      <c r="I9" s="10">
+      <c r="I10" s="10">
         <v>12487</v>
       </c>
-      <c r="J9" s="10">
-        <f>+J7+J8</f>
+      <c r="J10" s="10">
+        <f>+J8+J9</f>
         <v>13072</v>
       </c>
-      <c r="K9" s="10">
+      <c r="K10" s="10">
         <v>14054</v>
       </c>
-      <c r="L9" s="10">
+      <c r="L10" s="10">
         <v>14916</v>
       </c>
-      <c r="M9" s="10">
+      <c r="M10" s="10">
         <v>15004</v>
       </c>
-      <c r="N9" s="10">
+      <c r="N10" s="10">
         <v>15952</v>
       </c>
-      <c r="O9" s="12"/>
-      <c r="P9" s="12"/>
-      <c r="Q9" s="12"/>
-      <c r="R9" s="12"/>
-      <c r="S9" s="12"/>
-      <c r="T9" s="10">
-        <f>+T7+T8</f>
+      <c r="O10" s="10">
+        <v>18015</v>
+      </c>
+      <c r="P10" s="10">
+        <f>+P8+P9</f>
+        <v>19311</v>
+      </c>
+      <c r="Q10" s="10">
+        <v>22000</v>
+      </c>
+      <c r="R10" s="12"/>
+      <c r="S10" s="12"/>
+      <c r="T10" s="12"/>
+      <c r="U10" s="12"/>
+      <c r="V10" s="12"/>
+      <c r="W10" s="12"/>
+      <c r="X10" s="10">
+        <f>+X8+X9</f>
         <v>27450</v>
       </c>
-      <c r="U9" s="10">
-        <f>+U7+U8</f>
+      <c r="Y10" s="10">
+        <f>+Y8+Y9</f>
         <v>33203</v>
       </c>
-      <c r="V9" s="10">
-        <f>SUM(D9:G9)</f>
+      <c r="Z10" s="10">
+        <f>SUM(D10:G10)</f>
         <v>35819</v>
       </c>
-      <c r="W9" s="10">
+      <c r="AA10" s="10">
         <v>45000</v>
       </c>
-      <c r="X9" s="12"/>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
+      <c r="AB10" s="12"/>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C11" s="8">
         <v>2298</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D11" s="8">
         <v>2374</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E11" s="8">
         <v>2177</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F11" s="8">
         <v>2272</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G11" s="8">
         <v>2449</v>
       </c>
-      <c r="H10" s="8">
+      <c r="H11" s="8">
         <v>3114</v>
       </c>
-      <c r="I10" s="8">
+      <c r="I11" s="8">
         <v>3142</v>
       </c>
-      <c r="J10" s="8">
+      <c r="J11" s="8">
         <f>2434+699</f>
         <v>3133</v>
       </c>
-      <c r="K10" s="8">
+      <c r="K11" s="8">
         <v>3399</v>
       </c>
-      <c r="L10" s="8">
+      <c r="L11" s="8">
         <v>3273</v>
       </c>
-      <c r="M10" s="8">
+      <c r="M11" s="8">
         <v>3296</v>
       </c>
-      <c r="N10" s="8">
+      <c r="N11" s="8">
         <v>3704</v>
       </c>
-      <c r="T10" s="8">
+      <c r="O11" s="8">
+        <v>4213</v>
+      </c>
+      <c r="P11" s="8">
+        <f>4041+638</f>
+        <v>4679</v>
+      </c>
+      <c r="X11" s="8">
         <v>6555</v>
       </c>
-      <c r="U10" s="8">
+      <c r="Y11" s="8">
         <v>7629</v>
       </c>
-      <c r="V10" s="8">
-        <f>SUM(D10:G10)</f>
+      <c r="Z11" s="8">
+        <f>SUM(D11:G11)</f>
         <v>9272</v>
       </c>
-      <c r="W10" s="8">
-        <f>+W9*0.25</f>
+      <c r="AA11" s="8">
+        <f>+AA10*0.25</f>
         <v>11250</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="2" t="s">
+    <row r="12" spans="1:28" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="8">
-        <f t="shared" ref="C11:J11" si="0">+C9-C10</f>
+      <c r="C12" s="8">
+        <f t="shared" ref="C12:J12" si="0">+C10-C11</f>
         <v>6632</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D12" s="8">
         <f t="shared" si="0"/>
         <v>6541</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E12" s="8">
         <f t="shared" si="0"/>
         <v>6556</v>
       </c>
-      <c r="F11" s="8">
+      <c r="F12" s="8">
         <f t="shared" si="0"/>
         <v>6604</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G12" s="8">
         <f t="shared" si="0"/>
         <v>6846</v>
       </c>
-      <c r="H11" s="8">
+      <c r="H12" s="8">
         <f t="shared" si="0"/>
         <v>8847</v>
       </c>
-      <c r="I11" s="8">
+      <c r="I12" s="8">
         <f t="shared" si="0"/>
         <v>9345</v>
       </c>
-      <c r="J11" s="8">
+      <c r="J12" s="8">
         <f t="shared" si="0"/>
         <v>9939</v>
       </c>
-      <c r="K11" s="8">
-        <f>+K9-K10</f>
+      <c r="K12" s="8">
+        <f>+K10-K11</f>
         <v>10655</v>
       </c>
-      <c r="L11" s="8">
-        <f>+L9-L10</f>
+      <c r="L12" s="8">
+        <f>+L10-L11</f>
         <v>11643</v>
       </c>
-      <c r="M11" s="8">
-        <f t="shared" ref="M11" si="1">+M9-M10</f>
+      <c r="M12" s="8">
+        <f t="shared" ref="M12" si="1">+M10-M11</f>
         <v>11708</v>
       </c>
-      <c r="N11" s="8">
-        <f>+N9-N10</f>
+      <c r="N12" s="8">
+        <f>+N10-N11</f>
         <v>12248</v>
       </c>
-      <c r="O11" s="8"/>
-      <c r="P11" s="8"/>
-      <c r="Q11" s="8"/>
-      <c r="R11" s="8"/>
-      <c r="S11" s="8"/>
-      <c r="T11" s="8">
-        <f>+T9-T10</f>
+      <c r="O12" s="8">
+        <f>+O10-O11</f>
+        <v>13802</v>
+      </c>
+      <c r="P12" s="8">
+        <f>+P10-P11</f>
+        <v>14632</v>
+      </c>
+      <c r="Q12" s="8"/>
+      <c r="R12" s="8"/>
+      <c r="S12" s="8"/>
+      <c r="T12" s="8"/>
+      <c r="U12" s="8"/>
+      <c r="V12" s="8"/>
+      <c r="W12" s="8"/>
+      <c r="X12" s="8">
+        <f>+X10-X11</f>
         <v>20895</v>
       </c>
-      <c r="U11" s="8">
-        <f>+U9-U10</f>
+      <c r="Y12" s="8">
+        <f>+Y10-Y11</f>
         <v>25574</v>
       </c>
-      <c r="V11" s="8">
-        <f>+V9-V10</f>
+      <c r="Z12" s="8">
+        <f>+Z10-Z11</f>
         <v>26547</v>
       </c>
-      <c r="W11" s="8">
-        <f>+W9-W10</f>
+      <c r="AA12" s="8">
+        <f>+AA10-AA11</f>
         <v>33750</v>
       </c>
-      <c r="X11" s="8"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
+      <c r="AB12" s="8"/>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C13" s="8">
         <v>1197</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D13" s="8">
         <v>1195</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E13" s="8">
         <v>1312</v>
       </c>
-      <c r="F12" s="8">
+      <c r="F13" s="8">
         <v>1358</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G13" s="8">
         <v>1388</v>
       </c>
-      <c r="H12" s="8">
+      <c r="H13" s="8">
         <v>2308</v>
       </c>
-      <c r="I12" s="8">
+      <c r="I13" s="8">
         <v>2415</v>
       </c>
-      <c r="J12" s="8">
+      <c r="J13" s="8">
         <v>2353</v>
       </c>
-      <c r="K12" s="8">
+      <c r="K13" s="8">
         <v>2234</v>
       </c>
-      <c r="L12" s="8">
+      <c r="L13" s="8">
         <v>2253</v>
       </c>
-      <c r="M12" s="8">
+      <c r="M13" s="8">
         <v>2693</v>
       </c>
-      <c r="N12" s="8">
+      <c r="N13" s="8">
         <v>3050</v>
       </c>
-      <c r="T12" s="8">
+      <c r="O13" s="8">
+        <v>2981</v>
+      </c>
+      <c r="P13" s="8">
+        <v>2965</v>
+      </c>
+      <c r="X13" s="8">
         <v>4854</v>
       </c>
-      <c r="U12" s="8">
+      <c r="Y13" s="8">
         <v>4919</v>
       </c>
-      <c r="V12" s="8">
-        <f>SUM(D12:G12)</f>
+      <c r="Z13" s="8">
+        <f>SUM(D13:G13)</f>
         <v>5253</v>
       </c>
-      <c r="W12" s="8">
-        <f>+V12*1.1</f>
+      <c r="AA13" s="8">
+        <f>+Z13*1.1</f>
         <v>5778.3</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C14" s="8">
         <v>370</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D14" s="8">
         <v>348</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E14" s="8">
         <v>438</v>
       </c>
-      <c r="F13" s="8">
+      <c r="F14" s="8">
         <v>388</v>
       </c>
-      <c r="G13" s="8">
+      <c r="G14" s="8">
         <v>418</v>
       </c>
-      <c r="H13" s="8">
+      <c r="H14" s="8">
         <v>1572</v>
       </c>
-      <c r="I13" s="8">
+      <c r="I14" s="8">
         <v>1277</v>
       </c>
-      <c r="J13" s="8">
+      <c r="J14" s="8">
         <v>1100</v>
       </c>
-      <c r="K13" s="8">
+      <c r="K14" s="8">
         <v>1010</v>
       </c>
-      <c r="L13" s="8">
+      <c r="L14" s="8">
         <v>949</v>
       </c>
-      <c r="M13" s="8">
+      <c r="M14" s="8">
         <v>1083</v>
       </c>
-      <c r="N13" s="8">
+      <c r="N14" s="8">
         <v>1072</v>
       </c>
-      <c r="T13" s="8">
+      <c r="O14" s="8">
+        <v>1107</v>
+      </c>
+      <c r="P14" s="8">
+        <v>1019</v>
+      </c>
+      <c r="X14" s="8">
         <v>1347</v>
       </c>
-      <c r="U13" s="8">
+      <c r="Y14" s="8">
         <v>1382</v>
       </c>
-      <c r="V13" s="8">
-        <f>SUM(D13:G13)</f>
+      <c r="Z14" s="8">
+        <f>SUM(D14:G14)</f>
         <v>1592</v>
       </c>
-      <c r="W13" s="8">
-        <f>+V13*1.1</f>
+      <c r="AA14" s="8">
+        <f>+Z14*1.1</f>
         <v>1751.2</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="8">
-        <f t="shared" ref="C14:L14" si="2">+C12+C13</f>
+      <c r="C15" s="8">
+        <f t="shared" ref="C15:L15" si="2">+C13+C14</f>
         <v>1567</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D15" s="8">
         <f t="shared" si="2"/>
         <v>1543</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E15" s="8">
         <f t="shared" si="2"/>
         <v>1750</v>
       </c>
-      <c r="F14" s="8">
+      <c r="F15" s="8">
         <f t="shared" si="2"/>
         <v>1746</v>
       </c>
-      <c r="G14" s="8">
+      <c r="G15" s="8">
         <f t="shared" si="2"/>
         <v>1806</v>
       </c>
-      <c r="H14" s="8">
+      <c r="H15" s="8">
         <f t="shared" si="2"/>
         <v>3880</v>
       </c>
-      <c r="I14" s="8">
+      <c r="I15" s="8">
         <f t="shared" si="2"/>
         <v>3692</v>
       </c>
-      <c r="J14" s="8">
+      <c r="J15" s="8">
         <f t="shared" si="2"/>
         <v>3453</v>
       </c>
-      <c r="K14" s="8">
+      <c r="K15" s="8">
         <f t="shared" si="2"/>
         <v>3244</v>
       </c>
-      <c r="L14" s="8">
+      <c r="L15" s="8">
         <f t="shared" si="2"/>
         <v>3202</v>
       </c>
-      <c r="M14" s="8">
-        <f t="shared" ref="M14" si="3">+M12+M13</f>
+      <c r="M15" s="8">
+        <f t="shared" ref="M15" si="3">+M13+M14</f>
         <v>3776</v>
       </c>
-      <c r="N14" s="8">
-        <f t="shared" ref="M14:N14" si="4">+N12+N13</f>
+      <c r="N15" s="8">
+        <f t="shared" ref="N15:P15" si="4">+N13+N14</f>
         <v>4122</v>
       </c>
-      <c r="T14" s="8">
-        <f t="shared" ref="T14:U14" si="5">+T13+T12</f>
+      <c r="O15" s="8">
+        <f t="shared" si="4"/>
+        <v>4088</v>
+      </c>
+      <c r="P15" s="8">
+        <f t="shared" si="4"/>
+        <v>3984</v>
+      </c>
+      <c r="X15" s="8">
+        <f t="shared" ref="X15:Y15" si="5">+X14+X13</f>
         <v>6201</v>
       </c>
-      <c r="U14" s="8">
+      <c r="Y15" s="8">
         <f t="shared" si="5"/>
         <v>6301</v>
       </c>
-      <c r="V14" s="8">
-        <f>+V13+V12</f>
+      <c r="Z15" s="8">
+        <f>+Z14+Z13</f>
         <v>6845</v>
       </c>
-      <c r="W14" s="8">
-        <f>+W13+W12</f>
+      <c r="AA15" s="8">
+        <f>+AA14+AA13</f>
         <v>7529.5</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="8">
-        <f t="shared" ref="C15:L15" si="6">+C11-C14</f>
+      <c r="C16" s="8">
+        <f t="shared" ref="C16:L16" si="6">+C12-C15</f>
         <v>5065</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D16" s="8">
         <f t="shared" si="6"/>
         <v>4998</v>
       </c>
-      <c r="E15" s="8">
+      <c r="E16" s="8">
         <f t="shared" si="6"/>
         <v>4806</v>
       </c>
-      <c r="F15" s="8">
+      <c r="F16" s="8">
         <f t="shared" si="6"/>
         <v>4858</v>
       </c>
-      <c r="G15" s="8">
+      <c r="G16" s="8">
         <f t="shared" si="6"/>
         <v>5040</v>
       </c>
-      <c r="H15" s="8">
+      <c r="H16" s="8">
         <f t="shared" si="6"/>
         <v>4967</v>
       </c>
-      <c r="I15" s="8">
+      <c r="I16" s="8">
         <f t="shared" si="6"/>
         <v>5653</v>
       </c>
-      <c r="J15" s="8">
+      <c r="J16" s="8">
         <f t="shared" si="6"/>
         <v>6486</v>
       </c>
-      <c r="K15" s="8">
+      <c r="K16" s="8">
         <f t="shared" si="6"/>
         <v>7411</v>
       </c>
-      <c r="L15" s="8">
+      <c r="L16" s="8">
         <f t="shared" si="6"/>
         <v>8441</v>
       </c>
-      <c r="M15" s="8">
-        <f t="shared" ref="M15" si="7">+M11-M14</f>
+      <c r="M16" s="8">
+        <f t="shared" ref="M16" si="7">+M12-M15</f>
         <v>7932</v>
       </c>
-      <c r="N15" s="8">
-        <f t="shared" ref="M15:N15" si="8">+N11-N14</f>
+      <c r="N16" s="8">
+        <f t="shared" ref="N16:P16" si="8">+N12-N15</f>
         <v>8126</v>
       </c>
-      <c r="T15" s="8">
-        <f t="shared" ref="T15:U15" si="9">+T11-T14</f>
+      <c r="O16" s="8">
+        <f t="shared" si="8"/>
+        <v>9714</v>
+      </c>
+      <c r="P16" s="8">
+        <f t="shared" si="8"/>
+        <v>10648</v>
+      </c>
+      <c r="X16" s="8">
+        <f t="shared" ref="X16:Y16" si="9">+X12-X15</f>
         <v>14694</v>
       </c>
-      <c r="U15" s="8">
+      <c r="Y16" s="8">
         <f t="shared" si="9"/>
         <v>19273</v>
       </c>
-      <c r="V15" s="8">
-        <f>+V11-V14</f>
+      <c r="Z16" s="8">
+        <f>+Z12-Z15</f>
         <v>19702</v>
       </c>
-      <c r="W15" s="8">
-        <f>+W11-W14</f>
+      <c r="AA16" s="8">
+        <f>+AA12-AA15</f>
         <v>26220.5</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B16" t="s">
+    <row r="17" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C17" s="8">
         <f>-406+40</f>
         <v>-366</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D17" s="8">
         <f>-406-143</f>
         <v>-549</v>
       </c>
-      <c r="E16" s="8">
+      <c r="E17" s="8">
         <f>-405+113</f>
         <v>-292</v>
       </c>
-      <c r="F16" s="8">
+      <c r="F17" s="8">
         <f>-406+124</f>
         <v>-282</v>
       </c>
-      <c r="G16" s="8">
+      <c r="G17" s="8">
         <f>-405+132</f>
         <v>-273</v>
       </c>
-      <c r="H16" s="8">
+      <c r="H17" s="8">
         <f>-926+185</f>
         <v>-741</v>
       </c>
-      <c r="I16" s="8">
+      <c r="I17" s="8">
         <f>-1047+87</f>
         <v>-960</v>
       </c>
-      <c r="J16" s="8">
+      <c r="J17" s="8">
         <f>-1064+82</f>
         <v>-982</v>
       </c>
-      <c r="K16" s="8">
+      <c r="K17" s="8">
         <f>-916+52</f>
         <v>-864</v>
       </c>
-      <c r="L16" s="3">
+      <c r="L17" s="3">
         <f>-873+103</f>
         <v>-770</v>
       </c>
-      <c r="M16" s="3">
+      <c r="M17" s="3">
         <f>-769+25</f>
         <v>-744</v>
       </c>
-      <c r="N16" s="3">
+      <c r="N17" s="8">
         <f>-807+205</f>
         <v>-602</v>
       </c>
-      <c r="T16" s="8">
+      <c r="O17" s="8">
+        <f>-761+122</f>
+        <v>-639</v>
+      </c>
+      <c r="P17" s="8">
+        <v>-801</v>
+      </c>
+      <c r="X17" s="8">
         <f>-1885+131</f>
         <v>-1754</v>
       </c>
-      <c r="U16" s="8">
+      <c r="Y17" s="8">
         <f>-1737-54</f>
         <v>-1791</v>
       </c>
-      <c r="V16" s="8">
-        <f>SUM(D16:G16)</f>
+      <c r="Z17" s="8">
+        <f>SUM(D17:G17)</f>
         <v>-1396</v>
       </c>
-      <c r="W16" s="8">
-        <f>+V16</f>
+      <c r="AA17" s="8">
+        <f>+Z17</f>
         <v>-1396</v>
       </c>
     </row>
-    <row r="17" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B17" t="s">
+    <row r="18" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
         <v>23</v>
       </c>
-      <c r="C17" s="8">
-        <f t="shared" ref="C17:L17" si="10">+C15+C16</f>
+      <c r="C18" s="8">
+        <f t="shared" ref="C18:L18" si="10">+C16+C17</f>
         <v>4699</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D18" s="8">
         <f t="shared" si="10"/>
         <v>4449</v>
       </c>
-      <c r="E17" s="8">
+      <c r="E18" s="8">
         <f t="shared" si="10"/>
         <v>4514</v>
       </c>
-      <c r="F17" s="8">
+      <c r="F18" s="8">
         <f t="shared" si="10"/>
         <v>4576</v>
       </c>
-      <c r="G17" s="8">
+      <c r="G18" s="8">
         <f t="shared" si="10"/>
         <v>4767</v>
       </c>
-      <c r="H17" s="8">
+      <c r="H18" s="8">
         <f t="shared" si="10"/>
         <v>4226</v>
       </c>
-      <c r="I17" s="8">
+      <c r="I18" s="8">
         <f t="shared" si="10"/>
         <v>4693</v>
       </c>
-      <c r="J17" s="8">
+      <c r="J18" s="8">
         <f t="shared" si="10"/>
         <v>5504</v>
       </c>
-      <c r="K17" s="8">
+      <c r="K18" s="8">
         <f t="shared" si="10"/>
         <v>6547</v>
       </c>
-      <c r="L17" s="8">
+      <c r="L18" s="8">
         <f t="shared" si="10"/>
         <v>7671</v>
       </c>
-      <c r="M17" s="8">
-        <f t="shared" ref="M17" si="11">+M15+M16</f>
+      <c r="M18" s="8">
+        <f t="shared" ref="M18" si="11">+M16+M17</f>
         <v>7188</v>
       </c>
-      <c r="N17" s="8">
-        <f t="shared" ref="M17:N17" si="12">+N15+N16</f>
+      <c r="N18" s="8">
+        <f t="shared" ref="N18:P18" si="12">+N16+N17</f>
         <v>7524</v>
       </c>
-      <c r="T17" s="8">
-        <f>+T15+T16</f>
+      <c r="O18" s="8">
+        <f t="shared" si="12"/>
+        <v>9075</v>
+      </c>
+      <c r="P18" s="8">
+        <f t="shared" si="12"/>
+        <v>9847</v>
+      </c>
+      <c r="X18" s="8">
+        <f>+X16+X17</f>
         <v>12940</v>
       </c>
-      <c r="U17" s="8">
-        <f>+U15+U16</f>
+      <c r="Y18" s="8">
+        <f>+Y16+Y17</f>
         <v>17482</v>
       </c>
-      <c r="V17" s="8">
-        <f>+V15+V16</f>
+      <c r="Z18" s="8">
+        <f>+Z16+Z17</f>
         <v>18306</v>
       </c>
-      <c r="W17" s="8">
-        <f>+W15+W16</f>
+      <c r="AA18" s="8">
+        <f>+AA16+AA17</f>
         <v>24824.5</v>
       </c>
     </row>
-    <row r="18" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="2" t="s">
+    <row r="19" spans="2:28" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C19" s="8">
         <v>261</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D19" s="8">
         <v>66</v>
       </c>
-      <c r="E18" s="8">
+      <c r="E19" s="8">
         <v>235</v>
       </c>
-      <c r="F18" s="8">
+      <c r="F19" s="8">
         <v>271</v>
       </c>
-      <c r="G18" s="8">
+      <c r="G19" s="8">
         <v>443</v>
       </c>
-      <c r="H18" s="8">
+      <c r="H19" s="8">
         <f>68+735</f>
         <v>803</v>
       </c>
-      <c r="I18" s="8">
+      <c r="I19" s="8">
         <v>-116</v>
       </c>
-      <c r="J18" s="8">
+      <c r="J19" s="8">
         <v>4238</v>
       </c>
-      <c r="K18" s="8">
+      <c r="K19" s="8">
         <f>-442+1506</f>
         <v>1064</v>
       </c>
-      <c r="L18" s="8">
+      <c r="L19" s="8">
         <f>-12+1286</f>
         <v>1274</v>
       </c>
-      <c r="M18" s="8">
+      <c r="M19" s="8">
         <v>120</v>
       </c>
-      <c r="N18" s="8">
+      <c r="N19" s="8">
         <v>1145</v>
       </c>
-      <c r="O18" s="8"/>
-      <c r="P18" s="8"/>
-      <c r="Q18" s="8"/>
-      <c r="R18" s="8"/>
-      <c r="S18" s="8"/>
-      <c r="T18" s="8">
+      <c r="O19" s="8">
+        <v>0</v>
+      </c>
+      <c r="P19" s="8">
+        <v>846</v>
+      </c>
+      <c r="Q19" s="8"/>
+      <c r="R19" s="8"/>
+      <c r="S19" s="8"/>
+      <c r="T19" s="8"/>
+      <c r="U19" s="8"/>
+      <c r="V19" s="8"/>
+      <c r="W19" s="8"/>
+      <c r="X19" s="8">
         <f>29+299</f>
         <v>328</v>
       </c>
-      <c r="U18" s="8">
+      <c r="Y19" s="8">
         <f>939+272</f>
         <v>1211</v>
       </c>
-      <c r="V18" s="8">
-        <f>SUM(D18:G18)</f>
+      <c r="Z19" s="8">
+        <f>SUM(D19:G19)</f>
         <v>1015</v>
       </c>
-      <c r="W18" s="8">
-        <f>+W17*0.1</f>
+      <c r="AA19" s="8">
+        <f>+AA18*0.1</f>
         <v>2482.4500000000003</v>
       </c>
-      <c r="X18" s="8"/>
-    </row>
-    <row r="19" spans="2:24" ht="13" x14ac:dyDescent="0.3">
-      <c r="B19" t="s">
+      <c r="AB19" s="8"/>
+    </row>
+    <row r="20" spans="2:28" ht="13" x14ac:dyDescent="0.3">
+      <c r="B20" t="s">
         <v>25</v>
       </c>
-      <c r="C19" s="8">
-        <f t="shared" ref="C19:L19" si="13">+C17-C18</f>
+      <c r="C20" s="8">
+        <f t="shared" ref="C20:L20" si="13">+C18-C19</f>
         <v>4438</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D20" s="8">
         <f t="shared" si="13"/>
         <v>4383</v>
       </c>
-      <c r="E19" s="8">
+      <c r="E20" s="8">
         <f t="shared" si="13"/>
         <v>4279</v>
       </c>
-      <c r="F19" s="8">
+      <c r="F20" s="8">
         <f t="shared" si="13"/>
         <v>4305</v>
       </c>
-      <c r="G19" s="8">
+      <c r="G20" s="8">
         <f t="shared" si="13"/>
         <v>4324</v>
       </c>
-      <c r="H19" s="8">
+      <c r="H20" s="8">
         <f t="shared" si="13"/>
         <v>3423</v>
       </c>
-      <c r="I19" s="8">
+      <c r="I20" s="8">
         <f t="shared" si="13"/>
         <v>4809</v>
       </c>
-      <c r="J19" s="8">
+      <c r="J20" s="8">
         <f t="shared" si="13"/>
         <v>1266</v>
       </c>
-      <c r="K19" s="8">
+      <c r="K20" s="8">
         <f t="shared" si="13"/>
         <v>5483</v>
       </c>
-      <c r="L19" s="8">
+      <c r="L20" s="8">
         <f t="shared" si="13"/>
         <v>6397</v>
       </c>
-      <c r="M19" s="8">
-        <f t="shared" ref="M19" si="14">+M17-M18</f>
+      <c r="M20" s="8">
+        <f t="shared" ref="M20" si="14">+M18-M19</f>
         <v>7068</v>
       </c>
-      <c r="N19" s="8">
-        <f t="shared" ref="M19:N19" si="15">+N17-N18</f>
+      <c r="N20" s="8">
+        <f t="shared" ref="N20:P20" si="15">+N18-N19</f>
         <v>6379</v>
       </c>
-      <c r="T19" s="10">
-        <f>+T17-T18</f>
+      <c r="O20" s="8">
+        <f t="shared" si="15"/>
+        <v>9075</v>
+      </c>
+      <c r="P20" s="8">
+        <f t="shared" si="15"/>
+        <v>9001</v>
+      </c>
+      <c r="X20" s="10">
+        <f>+X18-X19</f>
         <v>12612</v>
       </c>
-      <c r="U19" s="10">
-        <f>+U17-U18</f>
+      <c r="Y20" s="10">
+        <f>+Y18-Y19</f>
         <v>16271</v>
       </c>
-      <c r="V19" s="10">
-        <f>+V17-V18</f>
+      <c r="Z20" s="10">
+        <f>+Z18-Z19</f>
         <v>17291</v>
       </c>
-      <c r="W19" s="10">
-        <f>+W17-W18</f>
+      <c r="AA20" s="10">
+        <f>+AA18-AA19</f>
         <v>22342.05</v>
       </c>
     </row>
-    <row r="20" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B20" t="s">
-        <v>75</v>
-      </c>
-      <c r="C20" s="11">
-        <f t="shared" ref="C20:L20" si="16">+C19/C21</f>
+    <row r="21" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" s="11">
+        <f t="shared" ref="C21:L21" si="16">+C20/C22</f>
         <v>1.0344988344988344</v>
       </c>
-      <c r="D20" s="11">
+      <c r="D21" s="11">
         <f t="shared" si="16"/>
         <v>1.0216783216783216</v>
       </c>
-      <c r="E20" s="11">
+      <c r="E21" s="11">
         <f t="shared" si="16"/>
         <v>1.0021077283372366</v>
       </c>
-      <c r="F20" s="11">
+      <c r="F21" s="11">
         <f t="shared" si="16"/>
         <v>1.0081967213114753</v>
       </c>
-      <c r="G20" s="11">
+      <c r="G21" s="11">
         <f t="shared" si="16"/>
         <v>1.0126463700234192</v>
       </c>
-      <c r="H20" s="11">
+      <c r="H21" s="11">
         <f t="shared" si="16"/>
         <v>0.73297644539614559</v>
       </c>
-      <c r="I20" s="11">
+      <c r="I21" s="11">
         <f t="shared" si="16"/>
         <v>1.0018750000000001</v>
       </c>
-      <c r="J20" s="11">
+      <c r="J21" s="11">
         <f t="shared" si="16"/>
         <v>0.27149903495603689</v>
       </c>
-      <c r="K20" s="11">
+      <c r="K21" s="11">
         <f t="shared" si="16"/>
         <v>1.1356669428334714</v>
       </c>
-      <c r="L20" s="11">
+      <c r="L21" s="11">
         <f t="shared" si="16"/>
         <v>1.3227874276261373</v>
       </c>
-      <c r="M20" s="11">
-        <f t="shared" ref="M20" si="17">+M19/M21</f>
+      <c r="M21" s="11">
+        <f t="shared" ref="M21" si="17">+M20/M22</f>
         <v>1.4645669291338583</v>
       </c>
-      <c r="N20" s="11">
-        <f t="shared" ref="M20:N20" si="18">+N19/N21</f>
+      <c r="N21" s="11">
+        <f t="shared" ref="N21:P21" si="18">+N20/N22</f>
         <v>1.312551440329218</v>
       </c>
-      <c r="T20" s="11">
-        <f>+T19/T21</f>
+      <c r="O21" s="11">
+        <f t="shared" si="18"/>
+        <v>1.8562078134587849</v>
+      </c>
+      <c r="P21" s="11">
+        <f t="shared" si="18"/>
+        <v>1.8414484451718494</v>
+      </c>
+      <c r="X21" s="11">
+        <f>+X20/X22</f>
         <v>2.9398601398601398</v>
       </c>
-      <c r="U20" s="11">
-        <f>+U19/U21</f>
+      <c r="Y21" s="11">
+        <f>+Y20/Y22</f>
         <v>3.8465721040189127</v>
       </c>
-      <c r="V20" s="11">
-        <f>+V19/V21</f>
+      <c r="Z21" s="11">
+        <f>+Z20/Z22</f>
         <v>3.9567505720823797</v>
       </c>
-      <c r="W20" s="11">
-        <f>+W19/W21</f>
+      <c r="AA21" s="11">
+        <f>+AA20/AA22</f>
         <v>4.6545937500000001</v>
       </c>
     </row>
-    <row r="21" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B21" t="s">
+    <row r="22" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
         <v>1</v>
       </c>
-      <c r="C21" s="8">
+      <c r="C22" s="8">
         <v>4290</v>
       </c>
-      <c r="D21" s="8">
+      <c r="D22" s="8">
         <v>4290</v>
       </c>
-      <c r="E21" s="8">
+      <c r="E22" s="8">
         <v>4270</v>
       </c>
-      <c r="F21" s="8">
+      <c r="F22" s="8">
         <v>4270</v>
       </c>
-      <c r="G21" s="8">
+      <c r="G22" s="8">
         <v>4270</v>
       </c>
-      <c r="H21" s="8">
+      <c r="H22" s="8">
         <v>4670</v>
       </c>
-      <c r="I21" s="8">
+      <c r="I22" s="8">
         <f>480*10</f>
         <v>4800</v>
       </c>
-      <c r="J21" s="8">
+      <c r="J22" s="8">
         <v>4663</v>
       </c>
-      <c r="K21" s="8">
+      <c r="K22" s="8">
         <v>4828</v>
       </c>
-      <c r="L21" s="8">
+      <c r="L22" s="8">
         <v>4836</v>
       </c>
-      <c r="M21" s="8">
+      <c r="M22" s="8">
         <v>4826</v>
       </c>
-      <c r="N21" s="8">
+      <c r="N22" s="8">
         <v>4860</v>
       </c>
-      <c r="T21" s="8">
+      <c r="O22" s="8">
+        <v>4889</v>
+      </c>
+      <c r="P22" s="8">
+        <v>4888</v>
+      </c>
+      <c r="X22" s="8">
         <v>4290</v>
       </c>
-      <c r="U21" s="8">
+      <c r="Y22" s="8">
         <v>4230</v>
       </c>
-      <c r="V21" s="8">
-        <f>AVERAGE(E21:H21)</f>
+      <c r="Z22" s="8">
+        <f>AVERAGE(E22:H22)</f>
         <v>4370</v>
       </c>
-      <c r="W21" s="8">
-        <f>+I21</f>
+      <c r="AA22" s="8">
+        <f>+I22</f>
         <v>4800</v>
       </c>
     </row>
-    <row r="25" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B25" t="s">
+    <row r="26" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
         <v>12</v>
       </c>
-      <c r="G25" s="9">
-        <f t="shared" ref="G25:L25" si="19">+G9/C9-1</f>
+      <c r="G26" s="9">
+        <f t="shared" ref="G26:L26" si="19">+G10/C10-1</f>
         <v>4.0873460246360516E-2</v>
       </c>
-      <c r="H25" s="9">
+      <c r="H26" s="9">
         <f t="shared" si="19"/>
         <v>0.34167134043746494</v>
       </c>
-      <c r="I25" s="9">
+      <c r="I26" s="9">
         <f t="shared" si="19"/>
         <v>0.42986373525707089</v>
       </c>
-      <c r="J25" s="9">
+      <c r="J26" s="9">
         <f t="shared" si="19"/>
         <v>0.47273546642631814</v>
       </c>
-      <c r="K25" s="9">
+      <c r="K26" s="9">
         <f t="shared" si="19"/>
         <v>0.51199569661108124</v>
       </c>
-      <c r="L25" s="9">
+      <c r="L26" s="9">
         <f t="shared" si="19"/>
         <v>0.24705292199648854</v>
       </c>
-      <c r="M25" s="9">
-        <f t="shared" ref="M25" si="20">+M9/I9-1</f>
+      <c r="M26" s="9">
+        <f t="shared" ref="M26" si="20">+M10/I10-1</f>
         <v>0.20156963241771453</v>
       </c>
-      <c r="N25" s="9">
-        <f t="shared" ref="N25" si="21">+N9/J9-1</f>
+      <c r="N26" s="9">
+        <f t="shared" ref="N26:Q26" si="21">+N10/J10-1</f>
         <v>0.2203182374541004</v>
       </c>
-      <c r="O25" s="9"/>
-      <c r="P25" s="9"/>
-      <c r="Q25" s="9"/>
-      <c r="R25" s="9"/>
-      <c r="U25" s="9">
-        <f>+U9/T9-1</f>
+      <c r="O26" s="9">
+        <f t="shared" si="21"/>
+        <v>0.2818414686210331</v>
+      </c>
+      <c r="P26" s="9">
+        <f t="shared" si="21"/>
+        <v>0.29465004022526142</v>
+      </c>
+      <c r="Q26" s="9">
+        <f t="shared" si="21"/>
+        <v>0.46627565982404695</v>
+      </c>
+      <c r="R26" s="9"/>
+      <c r="S26" s="9"/>
+      <c r="T26" s="9"/>
+      <c r="U26" s="9"/>
+      <c r="V26" s="9"/>
+      <c r="Y26" s="9">
+        <f>+Y10/X10-1</f>
         <v>0.20958105646630232</v>
       </c>
-      <c r="V25" s="9">
-        <f>+V9/U9-1</f>
+      <c r="Z26" s="9">
+        <f>+Z10/Y10-1</f>
         <v>7.8788061319760239E-2</v>
       </c>
-      <c r="W25" s="9">
-        <f>+W9/V9-1</f>
+      <c r="AA26" s="9">
+        <f>+AA10/Z10-1</f>
         <v>0.25631648008040431</v>
       </c>
     </row>
-    <row r="26" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B26" t="s">
+    <row r="27" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
         <v>15</v>
       </c>
-      <c r="C26" s="9">
-        <f t="shared" ref="C26:G26" si="22">+C11/C9</f>
+      <c r="C27" s="9">
+        <f t="shared" ref="C27:G27" si="22">+C12/C10</f>
         <v>0.7426651735722285</v>
       </c>
-      <c r="D26" s="9">
+      <c r="D27" s="9">
         <f t="shared" si="22"/>
         <v>0.7337072349971957</v>
       </c>
-      <c r="E26" s="9">
+      <c r="E27" s="9">
         <f t="shared" si="22"/>
         <v>0.75071567617084622</v>
       </c>
-      <c r="F26" s="9">
+      <c r="F27" s="9">
         <f t="shared" si="22"/>
         <v>0.74402884182063989</v>
       </c>
-      <c r="G26" s="9">
+      <c r="G27" s="9">
         <f t="shared" si="22"/>
         <v>0.7365250134480904</v>
       </c>
-      <c r="H26" s="9">
-        <f>+H11/H9</f>
+      <c r="H27" s="9">
+        <f>+H12/H10</f>
         <v>0.73965387509405567</v>
       </c>
-      <c r="I26" s="9">
-        <f>+I11/I9</f>
+      <c r="I27" s="9">
+        <f>+I12/I10</f>
         <v>0.74837831344598382</v>
       </c>
-      <c r="J26" s="9">
-        <f>+J11/J9</f>
+      <c r="J27" s="9">
+        <f>+J12/J10</f>
         <v>0.76032741738066101</v>
       </c>
-      <c r="K26" s="9">
-        <f>+K11/K9</f>
+      <c r="K27" s="9">
+        <f>+K12/K10</f>
         <v>0.75814714671979511</v>
       </c>
-      <c r="L26" s="9">
-        <f>+L11/L9</f>
+      <c r="L27" s="9">
+        <f>+L12/L10</f>
         <v>0.78057119871279168</v>
       </c>
-      <c r="M26" s="9">
-        <f t="shared" ref="M26:N26" si="23">+M11/M9</f>
+      <c r="M27" s="9">
+        <f t="shared" ref="M27:P27" si="23">+M12/M10</f>
         <v>0.78032524660090641</v>
       </c>
-      <c r="N26" s="9">
+      <c r="N27" s="9">
         <f t="shared" si="23"/>
         <v>0.7678034102306921</v>
       </c>
-      <c r="T26" s="9">
-        <f>+T11/T9</f>
+      <c r="O27" s="9">
+        <f t="shared" si="23"/>
+        <v>0.76613932833749654</v>
+      </c>
+      <c r="P27" s="9">
+        <f t="shared" si="23"/>
+        <v>0.75770286365284034</v>
+      </c>
+      <c r="X27" s="9">
+        <f>+X12/X10</f>
         <v>0.76120218579234977</v>
       </c>
-      <c r="U26" s="9">
-        <f>+U11/U9</f>
+      <c r="Y27" s="9">
+        <f>+Y12/Y10</f>
         <v>0.77023160557780923</v>
       </c>
-      <c r="V26" s="9">
-        <f>+V11/V9</f>
+      <c r="Z27" s="9">
+        <f>+Z12/Z10</f>
         <v>0.74114296881543318</v>
       </c>
-      <c r="W26" s="9">
-        <f>+W11/W9</f>
+      <c r="AA27" s="9">
+        <f>+AA12/AA10</f>
         <v>0.75</v>
       </c>
     </row>
-    <row r="27" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B27" t="s">
+    <row r="28" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
         <v>21</v>
       </c>
-      <c r="C27" s="9">
-        <f t="shared" ref="C27:G27" si="24">+C15/C9</f>
+      <c r="C28" s="9">
+        <f t="shared" ref="C28:G28" si="24">+C16/C10</f>
         <v>0.56718924972004481</v>
       </c>
-      <c r="D27" s="9">
+      <c r="D28" s="9">
         <f t="shared" si="24"/>
         <v>0.56062815479528882</v>
       </c>
-      <c r="E27" s="9">
+      <c r="E28" s="9">
         <f t="shared" si="24"/>
         <v>0.55032634833390592</v>
       </c>
-      <c r="F27" s="9">
+      <c r="F28" s="9">
         <f t="shared" si="24"/>
         <v>0.54731861198738174</v>
       </c>
-      <c r="G27" s="9">
+      <c r="G28" s="9">
         <f t="shared" si="24"/>
         <v>0.54222700376546529</v>
       </c>
-      <c r="H27" s="9">
-        <f>+H15/H9</f>
+      <c r="H28" s="9">
+        <f>+H16/H10</f>
         <v>0.41526628208343785</v>
       </c>
-      <c r="I27" s="9">
-        <f>+I15/I9</f>
+      <c r="I28" s="9">
+        <f>+I16/I10</f>
         <v>0.45271081925202211</v>
       </c>
-      <c r="J27" s="9">
-        <f>+J15/J9</f>
+      <c r="J28" s="9">
+        <f>+J16/J10</f>
         <v>0.49617503059975521</v>
       </c>
-      <c r="K27" s="9">
-        <f>+K15/K9</f>
+      <c r="K28" s="9">
+        <f>+K16/K10</f>
         <v>0.52732318201223849</v>
       </c>
-      <c r="L27" s="9">
-        <f>+L15/L9</f>
+      <c r="L28" s="9">
+        <f>+L16/L10</f>
         <v>0.56590238669884685</v>
       </c>
-      <c r="M27" s="9">
-        <f t="shared" ref="M27:N27" si="25">+M15/M9</f>
+      <c r="M28" s="9">
+        <f t="shared" ref="M28:P28" si="25">+M16/M10</f>
         <v>0.52865902426019729</v>
       </c>
-      <c r="N27" s="9">
+      <c r="N28" s="9">
         <f t="shared" si="25"/>
         <v>0.50940320962888663</v>
       </c>
-      <c r="T27" s="9">
-        <f>+T15/T9</f>
+      <c r="O28" s="9">
+        <f t="shared" si="25"/>
+        <v>0.53921731890091595</v>
+      </c>
+      <c r="P28" s="9">
+        <f t="shared" si="25"/>
+        <v>0.55139557765004399</v>
+      </c>
+      <c r="X28" s="9">
+        <f>+X16/X10</f>
         <v>0.53530054644808744</v>
       </c>
-      <c r="U27" s="9">
-        <f>+U15/U9</f>
+      <c r="Y28" s="9">
+        <f>+Y16/Y10</f>
         <v>0.58045959702436523</v>
       </c>
-      <c r="V27" s="9">
-        <f>+V15/V9</f>
+      <c r="Z28" s="9">
+        <f>+Z16/Z10</f>
         <v>0.55004327312320278</v>
       </c>
-      <c r="W27" s="9">
-        <f>+W15/W9</f>
+      <c r="AA28" s="9">
+        <f>+AA16/AA10</f>
         <v>0.58267777777777774</v>
       </c>
     </row>
-    <row r="30" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B30" t="s">
-        <v>87</v>
-      </c>
-      <c r="L30" s="8">
-        <f>+L31-L42</f>
+    <row r="31" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>86</v>
+      </c>
+      <c r="L31" s="8">
+        <f>+L32-L43</f>
         <v>-57272</v>
       </c>
-      <c r="M30" s="8">
-        <f>+M31-M42</f>
+      <c r="M31" s="8">
+        <f>+M32-M43</f>
         <v>0</v>
       </c>
-      <c r="N30" s="8">
-        <f>+N31-N42</f>
+      <c r="N31" s="8">
+        <f>+N32-N43</f>
         <v>-53511</v>
       </c>
-    </row>
-    <row r="31" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="2" t="s">
+      <c r="O31" s="8">
+        <f>+O32-O43</f>
+        <v>-48958</v>
+      </c>
+      <c r="P31" s="8">
+        <f>+P32-P43</f>
+        <v>-51883</v>
+      </c>
+    </row>
+    <row r="32" spans="2:28" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="2" t="s">
         <v>3</v>
-      </c>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="8">
-        <v>11864</v>
-      </c>
-      <c r="I31" s="8">
-        <v>9809</v>
-      </c>
-      <c r="J31" s="8">
-        <v>9952</v>
-      </c>
-      <c r="K31" s="8"/>
-      <c r="L31" s="8">
-        <v>9307</v>
-      </c>
-      <c r="M31" s="8"/>
-      <c r="N31" s="8">
-        <v>10718</v>
-      </c>
-      <c r="O31" s="8"/>
-      <c r="P31" s="8"/>
-      <c r="Q31" s="8"/>
-      <c r="R31" s="8"/>
-      <c r="S31" s="8"/>
-      <c r="T31" s="8"/>
-      <c r="U31" s="8"/>
-      <c r="V31" s="8"/>
-      <c r="W31" s="8"/>
-      <c r="X31" s="8"/>
-    </row>
-    <row r="32" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
@@ -2315,24 +2633,28 @@
       <c r="F32" s="8"/>
       <c r="G32" s="8"/>
       <c r="H32" s="8">
-        <v>4969</v>
+        <v>11864</v>
       </c>
       <c r="I32" s="8">
-        <v>5500</v>
+        <v>9809</v>
       </c>
       <c r="J32" s="8">
-        <v>4665</v>
+        <v>9952</v>
       </c>
       <c r="K32" s="8"/>
       <c r="L32" s="8">
-        <v>4955</v>
+        <v>9307</v>
       </c>
       <c r="M32" s="8"/>
       <c r="N32" s="8">
-        <v>6494</v>
-      </c>
-      <c r="O32" s="8"/>
-      <c r="P32" s="8"/>
+        <v>10718</v>
+      </c>
+      <c r="O32" s="8">
+        <v>16178</v>
+      </c>
+      <c r="P32" s="8">
+        <v>14174</v>
+      </c>
       <c r="Q32" s="8"/>
       <c r="R32" s="8"/>
       <c r="S32" s="8"/>
@@ -2341,10 +2663,14 @@
       <c r="V32" s="8"/>
       <c r="W32" s="8"/>
       <c r="X32" s="8"/>
-    </row>
-    <row r="33" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Y32" s="8"/>
+      <c r="Z32" s="8"/>
+      <c r="AA32" s="8"/>
+      <c r="AB32" s="8"/>
+    </row>
+    <row r="33" spans="2:28" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B33" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
@@ -2352,24 +2678,28 @@
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="8">
-        <v>1920</v>
+        <v>4969</v>
       </c>
       <c r="I33" s="8">
-        <v>1842</v>
+        <v>5500</v>
       </c>
       <c r="J33" s="8">
-        <v>1894</v>
+        <v>4665</v>
       </c>
       <c r="K33" s="8"/>
       <c r="L33" s="8">
-        <v>1908</v>
+        <v>4955</v>
       </c>
       <c r="M33" s="8"/>
       <c r="N33" s="8">
-        <v>2180</v>
-      </c>
-      <c r="O33" s="8"/>
-      <c r="P33" s="8"/>
+        <v>6494</v>
+      </c>
+      <c r="O33" s="8">
+        <v>7145</v>
+      </c>
+      <c r="P33" s="8">
+        <v>8460</v>
+      </c>
       <c r="Q33" s="8"/>
       <c r="R33" s="8"/>
       <c r="S33" s="8"/>
@@ -2378,10 +2708,14 @@
       <c r="V33" s="8"/>
       <c r="W33" s="8"/>
       <c r="X33" s="8"/>
-    </row>
-    <row r="34" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Y33" s="8"/>
+      <c r="Z33" s="8"/>
+      <c r="AA33" s="8"/>
+      <c r="AB33" s="8"/>
+    </row>
+    <row r="34" spans="2:28" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B34" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
@@ -2389,24 +2723,28 @@
       <c r="F34" s="8"/>
       <c r="G34" s="8"/>
       <c r="H34" s="8">
-        <v>8439</v>
+        <v>1920</v>
       </c>
       <c r="I34" s="8">
-        <v>8151</v>
+        <v>1842</v>
       </c>
       <c r="J34" s="8">
-        <v>3436</v>
+        <v>1894</v>
       </c>
       <c r="K34" s="8"/>
       <c r="L34" s="8">
-        <v>4820</v>
+        <v>1908</v>
       </c>
       <c r="M34" s="8"/>
       <c r="N34" s="8">
-        <v>5606</v>
-      </c>
-      <c r="O34" s="8"/>
-      <c r="P34" s="8"/>
+        <v>2180</v>
+      </c>
+      <c r="O34" s="8">
+        <v>2270</v>
+      </c>
+      <c r="P34" s="8">
+        <v>2962</v>
+      </c>
       <c r="Q34" s="8"/>
       <c r="R34" s="8"/>
       <c r="S34" s="8"/>
@@ -2415,10 +2753,14 @@
       <c r="V34" s="8"/>
       <c r="W34" s="8"/>
       <c r="X34" s="8"/>
-    </row>
-    <row r="35" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Y34" s="8"/>
+      <c r="Z34" s="8"/>
+      <c r="AA34" s="8"/>
+      <c r="AB34" s="8"/>
+    </row>
+    <row r="35" spans="2:28" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B35" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C35" s="8"/>
       <c r="D35" s="8"/>
@@ -2426,24 +2768,28 @@
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="8">
-        <v>2662</v>
+        <v>8439</v>
       </c>
       <c r="I35" s="8">
-        <v>2668</v>
+        <v>8151</v>
       </c>
       <c r="J35" s="8">
-        <v>2602</v>
+        <v>3436</v>
       </c>
       <c r="K35" s="8"/>
       <c r="L35" s="8">
-        <v>2465</v>
+        <v>4820</v>
       </c>
       <c r="M35" s="8"/>
       <c r="N35" s="8">
-        <v>2451</v>
-      </c>
-      <c r="O35" s="8"/>
-      <c r="P35" s="8"/>
+        <v>5606</v>
+      </c>
+      <c r="O35" s="8">
+        <v>5980</v>
+      </c>
+      <c r="P35" s="8">
+        <v>6466</v>
+      </c>
       <c r="Q35" s="8"/>
       <c r="R35" s="8"/>
       <c r="S35" s="8"/>
@@ -2452,10 +2798,14 @@
       <c r="V35" s="8"/>
       <c r="W35" s="8"/>
       <c r="X35" s="8"/>
-    </row>
-    <row r="36" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Y35" s="8"/>
+      <c r="Z35" s="8"/>
+      <c r="AA35" s="8"/>
+      <c r="AB35" s="8"/>
+    </row>
+    <row r="36" spans="2:28" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B36" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C36" s="8"/>
       <c r="D36" s="8"/>
@@ -2463,29 +2813,28 @@
       <c r="F36" s="8"/>
       <c r="G36" s="8"/>
       <c r="H36" s="8">
-        <f>97586+47185</f>
-        <v>144771</v>
+        <v>2662</v>
       </c>
       <c r="I36" s="8">
-        <f>97873+45407</f>
-        <v>143280</v>
+        <v>2668</v>
       </c>
       <c r="J36" s="8">
-        <f>97873+43034</f>
-        <v>140907</v>
+        <v>2602</v>
       </c>
       <c r="K36" s="8"/>
       <c r="L36" s="8">
-        <f>97871+38583</f>
-        <v>136454</v>
+        <v>2465</v>
       </c>
       <c r="M36" s="8"/>
       <c r="N36" s="8">
-        <f>97801+34344</f>
-        <v>132145</v>
-      </c>
-      <c r="O36" s="8"/>
-      <c r="P36" s="8"/>
+        <v>2451</v>
+      </c>
+      <c r="O36" s="8">
+        <v>2530</v>
+      </c>
+      <c r="P36" s="8">
+        <v>2599</v>
+      </c>
       <c r="Q36" s="8"/>
       <c r="R36" s="8"/>
       <c r="S36" s="8"/>
@@ -2494,10 +2843,14 @@
       <c r="V36" s="8"/>
       <c r="W36" s="8"/>
       <c r="X36" s="8"/>
-    </row>
-    <row r="37" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Y36" s="8"/>
+      <c r="Z36" s="8"/>
+      <c r="AA36" s="8"/>
+      <c r="AB36" s="8"/>
+    </row>
+    <row r="37" spans="2:28" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B37" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C37" s="8"/>
       <c r="D37" s="8"/>
@@ -2505,24 +2858,35 @@
       <c r="F37" s="8"/>
       <c r="G37" s="8"/>
       <c r="H37" s="8">
-        <v>3245</v>
+        <f>97586+47185</f>
+        <v>144771</v>
       </c>
       <c r="I37" s="8">
-        <v>3961</v>
+        <f>97873+45407</f>
+        <v>143280</v>
       </c>
       <c r="J37" s="8">
-        <v>4510</v>
+        <f>97873+43034</f>
+        <v>140907</v>
       </c>
       <c r="K37" s="8"/>
       <c r="L37" s="8">
-        <v>5449</v>
+        <f>97871+38583</f>
+        <v>136454</v>
       </c>
       <c r="M37" s="8"/>
       <c r="N37" s="8">
-        <v>6027</v>
-      </c>
-      <c r="O37" s="8"/>
-      <c r="P37" s="8"/>
+        <f>97801+34344</f>
+        <v>132145</v>
+      </c>
+      <c r="O37" s="8">
+        <f>97801+32273</f>
+        <v>130074</v>
+      </c>
+      <c r="P37" s="8">
+        <f>97801+30302</f>
+        <v>128103</v>
+      </c>
       <c r="Q37" s="8"/>
       <c r="R37" s="8"/>
       <c r="S37" s="8"/>
@@ -2531,10 +2895,14 @@
       <c r="V37" s="8"/>
       <c r="W37" s="8"/>
       <c r="X37" s="8"/>
-    </row>
-    <row r="38" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Y37" s="8"/>
+      <c r="Z37" s="8"/>
+      <c r="AA37" s="8"/>
+      <c r="AB37" s="8"/>
+    </row>
+    <row r="38" spans="2:28" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B38" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C38" s="8"/>
       <c r="D38" s="8"/>
@@ -2542,35 +2910,28 @@
       <c r="F38" s="8"/>
       <c r="G38" s="8"/>
       <c r="H38" s="8">
-        <f>SUM(H31:H37)</f>
-        <v>177870</v>
+        <v>3245</v>
       </c>
       <c r="I38" s="8">
-        <f>SUM(I31:I37)</f>
-        <v>175211</v>
+        <v>3961</v>
       </c>
       <c r="J38" s="8">
-        <f>SUM(J31:J37)</f>
-        <v>167966</v>
-      </c>
-      <c r="K38" s="8">
-        <f>SUM(K31:K37)</f>
-        <v>0</v>
-      </c>
+        <v>4510</v>
+      </c>
+      <c r="K38" s="8"/>
       <c r="L38" s="8">
-        <f>SUM(L31:L37)</f>
-        <v>165358</v>
-      </c>
-      <c r="M38" s="8">
-        <f>SUM(M31:M37)</f>
-        <v>0</v>
-      </c>
+        <v>5449</v>
+      </c>
+      <c r="M38" s="8"/>
       <c r="N38" s="8">
-        <f>SUM(N31:N37)</f>
-        <v>165621</v>
-      </c>
-      <c r="O38" s="8"/>
-      <c r="P38" s="8"/>
+        <v>6027</v>
+      </c>
+      <c r="O38" s="8">
+        <v>6915</v>
+      </c>
+      <c r="P38" s="8">
+        <v>7139</v>
+      </c>
       <c r="Q38" s="8"/>
       <c r="R38" s="8"/>
       <c r="S38" s="8"/>
@@ -2579,22 +2940,56 @@
       <c r="V38" s="8"/>
       <c r="W38" s="8"/>
       <c r="X38" s="8"/>
-    </row>
-    <row r="39" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Y38" s="8"/>
+      <c r="Z38" s="8"/>
+      <c r="AA38" s="8"/>
+      <c r="AB38" s="8"/>
+    </row>
+    <row r="39" spans="2:28" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="C39" s="8"/>
       <c r="D39" s="8"/>
       <c r="E39" s="8"/>
       <c r="F39" s="8"/>
       <c r="G39" s="8"/>
-      <c r="H39" s="8"/>
-      <c r="I39" s="8"/>
-      <c r="J39" s="8"/>
-      <c r="K39" s="8"/>
-      <c r="L39" s="8"/>
-      <c r="M39" s="8"/>
-      <c r="N39" s="8"/>
-      <c r="O39" s="8"/>
-      <c r="P39" s="8"/>
+      <c r="H39" s="8">
+        <f t="shared" ref="H39:P39" si="26">SUM(H32:H38)</f>
+        <v>177870</v>
+      </c>
+      <c r="I39" s="8">
+        <f t="shared" si="26"/>
+        <v>175211</v>
+      </c>
+      <c r="J39" s="8">
+        <f t="shared" si="26"/>
+        <v>167966</v>
+      </c>
+      <c r="K39" s="8">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="L39" s="8">
+        <f t="shared" si="26"/>
+        <v>165358</v>
+      </c>
+      <c r="M39" s="8">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="N39" s="8">
+        <f t="shared" si="26"/>
+        <v>165621</v>
+      </c>
+      <c r="O39" s="8">
+        <f t="shared" si="26"/>
+        <v>171092</v>
+      </c>
+      <c r="P39" s="8">
+        <f t="shared" si="26"/>
+        <v>169903</v>
+      </c>
       <c r="Q39" s="8"/>
       <c r="R39" s="8"/>
       <c r="S39" s="8"/>
@@ -2603,33 +2998,24 @@
       <c r="V39" s="8"/>
       <c r="W39" s="8"/>
       <c r="X39" s="8"/>
-    </row>
-    <row r="40" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="2" t="s">
-        <v>33</v>
-      </c>
+      <c r="Y39" s="8"/>
+      <c r="Z39" s="8"/>
+      <c r="AA39" s="8"/>
+      <c r="AB39" s="8"/>
+    </row>
+    <row r="40" spans="2:28" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C40" s="8"/>
       <c r="D40" s="8"/>
       <c r="E40" s="8"/>
       <c r="F40" s="8"/>
       <c r="G40" s="8"/>
-      <c r="H40" s="8">
-        <v>1496</v>
-      </c>
-      <c r="I40" s="8">
-        <v>1441</v>
-      </c>
-      <c r="J40" s="8">
-        <v>1757</v>
-      </c>
+      <c r="H40" s="8"/>
+      <c r="I40" s="8"/>
+      <c r="J40" s="8"/>
       <c r="K40" s="8"/>
-      <c r="L40" s="8">
-        <v>1905</v>
-      </c>
+      <c r="L40" s="8"/>
       <c r="M40" s="8"/>
-      <c r="N40" s="8">
-        <v>1432</v>
-      </c>
+      <c r="N40" s="8"/>
       <c r="O40" s="8"/>
       <c r="P40" s="8"/>
       <c r="Q40" s="8"/>
@@ -2640,10 +3026,14 @@
       <c r="V40" s="8"/>
       <c r="W40" s="8"/>
       <c r="X40" s="8"/>
-    </row>
-    <row r="41" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Y40" s="8"/>
+      <c r="Z40" s="8"/>
+      <c r="AA40" s="8"/>
+      <c r="AB40" s="8"/>
+    </row>
+    <row r="41" spans="2:28" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B41" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C41" s="8"/>
       <c r="D41" s="8"/>
@@ -2651,24 +3041,28 @@
       <c r="F41" s="8"/>
       <c r="G41" s="8"/>
       <c r="H41" s="8">
-        <v>1128</v>
+        <v>1496</v>
       </c>
       <c r="I41" s="8">
-        <v>1385</v>
+        <v>1441</v>
       </c>
       <c r="J41" s="8">
-        <v>1725</v>
+        <v>1757</v>
       </c>
       <c r="K41" s="8"/>
       <c r="L41" s="8">
-        <v>922</v>
+        <v>1905</v>
       </c>
       <c r="M41" s="8"/>
       <c r="N41" s="8">
-        <v>1719</v>
-      </c>
-      <c r="O41" s="8"/>
-      <c r="P41" s="8"/>
+        <v>1432</v>
+      </c>
+      <c r="O41" s="8">
+        <v>1560</v>
+      </c>
+      <c r="P41" s="8">
+        <v>2112</v>
+      </c>
       <c r="Q41" s="8"/>
       <c r="R41" s="8"/>
       <c r="S41" s="8"/>
@@ -2677,10 +3071,14 @@
       <c r="V41" s="8"/>
       <c r="W41" s="8"/>
       <c r="X41" s="8"/>
-    </row>
-    <row r="42" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Y41" s="8"/>
+      <c r="Z41" s="8"/>
+      <c r="AA41" s="8"/>
+      <c r="AB41" s="8"/>
+    </row>
+    <row r="42" spans="2:28" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B42" s="2" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="C42" s="8"/>
       <c r="D42" s="8"/>
@@ -2688,29 +3086,28 @@
       <c r="F42" s="8"/>
       <c r="G42" s="8"/>
       <c r="H42" s="8">
-        <f>2433+73468</f>
-        <v>75901</v>
+        <v>1128</v>
       </c>
       <c r="I42" s="8">
-        <f>2426+71590</f>
-        <v>74016</v>
+        <v>1385</v>
       </c>
       <c r="J42" s="8">
-        <f>12578+66798</f>
-        <v>79376</v>
+        <v>1725</v>
       </c>
       <c r="K42" s="8"/>
       <c r="L42" s="8">
-        <f>5653+60926</f>
-        <v>66579</v>
+        <v>922</v>
       </c>
       <c r="M42" s="8"/>
       <c r="N42" s="8">
-        <f>1399+62830</f>
-        <v>64229</v>
-      </c>
-      <c r="O42" s="8"/>
-      <c r="P42" s="8"/>
+        <v>1719</v>
+      </c>
+      <c r="O42" s="8">
+        <v>2129</v>
+      </c>
+      <c r="P42" s="8">
+        <v>864</v>
+      </c>
       <c r="Q42" s="8"/>
       <c r="R42" s="8"/>
       <c r="S42" s="8"/>
@@ -2719,10 +3116,14 @@
       <c r="V42" s="8"/>
       <c r="W42" s="8"/>
       <c r="X42" s="8"/>
-    </row>
-    <row r="43" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Y42" s="8"/>
+      <c r="Z42" s="8"/>
+      <c r="AA42" s="8"/>
+      <c r="AB42" s="8"/>
+    </row>
+    <row r="43" spans="2:28" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B43" s="2" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
@@ -2730,24 +3131,35 @@
       <c r="F43" s="8"/>
       <c r="G43" s="8"/>
       <c r="H43" s="8">
-        <v>15312</v>
+        <f>2433+73468</f>
+        <v>75901</v>
       </c>
       <c r="I43" s="8">
-        <v>14919</v>
+        <f>2426+71590</f>
+        <v>74016</v>
       </c>
       <c r="J43" s="8">
-        <v>3161</v>
+        <f>12578+66798</f>
+        <v>79376</v>
       </c>
       <c r="K43" s="8"/>
       <c r="L43" s="8">
-        <v>12430</v>
+        <f>5653+60926</f>
+        <v>66579</v>
       </c>
       <c r="M43" s="8"/>
       <c r="N43" s="8">
-        <v>12154</v>
-      </c>
-      <c r="O43" s="8"/>
-      <c r="P43" s="8"/>
+        <f>1399+62830</f>
+        <v>64229</v>
+      </c>
+      <c r="O43" s="8">
+        <f>3152+61984</f>
+        <v>65136</v>
+      </c>
+      <c r="P43" s="8">
+        <f>2252+63805</f>
+        <v>66057</v>
+      </c>
       <c r="Q43" s="8"/>
       <c r="R43" s="8"/>
       <c r="S43" s="8"/>
@@ -2756,10 +3168,14 @@
       <c r="V43" s="8"/>
       <c r="W43" s="8"/>
       <c r="X43" s="8"/>
-    </row>
-    <row r="44" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Y43" s="8"/>
+      <c r="Z43" s="8"/>
+      <c r="AA43" s="8"/>
+      <c r="AB43" s="8"/>
+    </row>
+    <row r="44" spans="2:28" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B44" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C44" s="8"/>
       <c r="D44" s="8"/>
@@ -2767,24 +3183,28 @@
       <c r="F44" s="8"/>
       <c r="G44" s="8"/>
       <c r="H44" s="8">
-        <v>13749</v>
+        <v>15312</v>
       </c>
       <c r="I44" s="8">
-        <v>13489</v>
+        <v>14919</v>
       </c>
       <c r="J44" s="8">
-        <v>16296</v>
+        <v>3161</v>
       </c>
       <c r="K44" s="8"/>
       <c r="L44" s="8">
-        <v>13733</v>
+        <v>12430</v>
       </c>
       <c r="M44" s="8"/>
       <c r="N44" s="8">
-        <v>12810</v>
-      </c>
-      <c r="O44" s="8"/>
-      <c r="P44" s="8"/>
+        <v>12154</v>
+      </c>
+      <c r="O44" s="8">
+        <v>11673</v>
+      </c>
+      <c r="P44" s="8">
+        <v>11631</v>
+      </c>
       <c r="Q44" s="8"/>
       <c r="R44" s="8"/>
       <c r="S44" s="8"/>
@@ -2793,10 +3213,14 @@
       <c r="V44" s="8"/>
       <c r="W44" s="8"/>
       <c r="X44" s="8"/>
-    </row>
-    <row r="45" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Y44" s="8"/>
+      <c r="Z44" s="8"/>
+      <c r="AA44" s="8"/>
+      <c r="AB44" s="8"/>
+    </row>
+    <row r="45" spans="2:28" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B45" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C45" s="8"/>
       <c r="D45" s="8"/>
@@ -2804,24 +3228,28 @@
       <c r="F45" s="8"/>
       <c r="G45" s="8"/>
       <c r="H45" s="8">
-        <v>70284</v>
+        <v>13749</v>
       </c>
       <c r="I45" s="8">
-        <v>69961</v>
+        <v>13489</v>
       </c>
       <c r="J45" s="8">
-        <v>65651</v>
+        <v>16296</v>
       </c>
       <c r="K45" s="8"/>
       <c r="L45" s="8">
-        <v>69789</v>
+        <v>13733</v>
       </c>
       <c r="M45" s="8"/>
       <c r="N45" s="8">
-        <v>73277</v>
-      </c>
-      <c r="O45" s="8"/>
-      <c r="P45" s="8"/>
+        <v>12810</v>
+      </c>
+      <c r="O45" s="8">
+        <v>9302</v>
+      </c>
+      <c r="P45" s="8">
+        <v>9367</v>
+      </c>
       <c r="Q45" s="8"/>
       <c r="R45" s="8"/>
       <c r="S45" s="8"/>
@@ -2830,10 +3258,14 @@
       <c r="V45" s="8"/>
       <c r="W45" s="8"/>
       <c r="X45" s="8"/>
-    </row>
-    <row r="46" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Y45" s="8"/>
+      <c r="Z45" s="8"/>
+      <c r="AA45" s="8"/>
+      <c r="AB45" s="8"/>
+    </row>
+    <row r="46" spans="2:28" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B46" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C46" s="8"/>
       <c r="D46" s="8"/>
@@ -2841,35 +3273,28 @@
       <c r="F46" s="8"/>
       <c r="G46" s="8"/>
       <c r="H46" s="8">
-        <f>SUM(H40:H45)</f>
-        <v>177870</v>
+        <v>70284</v>
       </c>
       <c r="I46" s="8">
-        <f>SUM(I40:I45)</f>
-        <v>175211</v>
+        <v>69961</v>
       </c>
       <c r="J46" s="8">
-        <f>SUM(J40:J45)</f>
-        <v>167966</v>
-      </c>
-      <c r="K46" s="8">
-        <f>SUM(K40:K45)</f>
-        <v>0</v>
-      </c>
+        <v>65651</v>
+      </c>
+      <c r="K46" s="8"/>
       <c r="L46" s="8">
-        <f>SUM(L40:L45)</f>
-        <v>165358</v>
-      </c>
-      <c r="M46" s="8">
-        <f t="shared" ref="M46:N46" si="26">SUM(M40:M45)</f>
-        <v>0</v>
-      </c>
+        <v>69789</v>
+      </c>
+      <c r="M46" s="8"/>
       <c r="N46" s="8">
-        <f t="shared" si="26"/>
-        <v>165621</v>
-      </c>
-      <c r="O46" s="8"/>
-      <c r="P46" s="8"/>
+        <v>73277</v>
+      </c>
+      <c r="O46" s="8">
+        <v>81292</v>
+      </c>
+      <c r="P46" s="8">
+        <v>79872</v>
+      </c>
       <c r="Q46" s="8"/>
       <c r="R46" s="8"/>
       <c r="S46" s="8"/>
@@ -2878,276 +3303,346 @@
       <c r="V46" s="8"/>
       <c r="W46" s="8"/>
       <c r="X46" s="8"/>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B48" t="s">
+      <c r="Y46" s="8"/>
+      <c r="Z46" s="8"/>
+      <c r="AA46" s="8"/>
+      <c r="AB46" s="8"/>
+    </row>
+    <row r="47" spans="2:28" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C47" s="8"/>
+      <c r="D47" s="8"/>
+      <c r="E47" s="8"/>
+      <c r="F47" s="8"/>
+      <c r="G47" s="8"/>
+      <c r="H47" s="8">
+        <f>SUM(H41:H46)</f>
+        <v>177870</v>
+      </c>
+      <c r="I47" s="8">
+        <f>SUM(I41:I46)</f>
+        <v>175211</v>
+      </c>
+      <c r="J47" s="8">
+        <f>SUM(J41:J46)</f>
+        <v>167966</v>
+      </c>
+      <c r="K47" s="8">
+        <f>SUM(K41:K46)</f>
+        <v>0</v>
+      </c>
+      <c r="L47" s="8">
+        <f>SUM(L41:L46)</f>
+        <v>165358</v>
+      </c>
+      <c r="M47" s="8">
+        <f t="shared" ref="M47:P47" si="27">SUM(M41:M46)</f>
+        <v>0</v>
+      </c>
+      <c r="N47" s="8">
+        <f t="shared" si="27"/>
+        <v>165621</v>
+      </c>
+      <c r="O47" s="8">
+        <f t="shared" si="27"/>
+        <v>171092</v>
+      </c>
+      <c r="P47" s="8">
+        <f t="shared" si="27"/>
+        <v>169903</v>
+      </c>
+      <c r="Q47" s="8"/>
+      <c r="R47" s="8"/>
+      <c r="S47" s="8"/>
+      <c r="T47" s="8"/>
+      <c r="U47" s="8"/>
+      <c r="V47" s="8"/>
+      <c r="W47" s="8"/>
+      <c r="X47" s="8"/>
+      <c r="Y47" s="8"/>
+      <c r="Z47" s="8"/>
+      <c r="AA47" s="8"/>
+      <c r="AB47" s="8"/>
+    </row>
+    <row r="49" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B49" t="s">
         <v>39</v>
       </c>
-      <c r="H48" s="8">
-        <f>+H19</f>
+      <c r="H49" s="8">
+        <f t="shared" ref="H49:P49" si="28">+H20</f>
         <v>3423</v>
       </c>
-      <c r="I48" s="8">
-        <f>+I19</f>
+      <c r="I49" s="8">
+        <f t="shared" si="28"/>
         <v>4809</v>
       </c>
-      <c r="J48" s="8">
-        <f>+J19</f>
+      <c r="J49" s="8">
+        <f t="shared" si="28"/>
         <v>1266</v>
       </c>
-      <c r="K48" s="8">
-        <f>+K19</f>
+      <c r="K49" s="8">
+        <f t="shared" si="28"/>
         <v>5483</v>
       </c>
-      <c r="L48" s="8">
-        <f>+L19</f>
+      <c r="L49" s="8">
+        <f t="shared" si="28"/>
         <v>6397</v>
       </c>
-      <c r="M48" s="8">
-        <f>+M19</f>
+      <c r="M49" s="8">
+        <f t="shared" si="28"/>
         <v>7068</v>
       </c>
-      <c r="N48" s="8">
-        <f>+N19</f>
+      <c r="N49" s="8">
+        <f t="shared" si="28"/>
         <v>6379</v>
       </c>
-    </row>
-    <row r="49" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B49" t="s">
+      <c r="O49" s="8">
+        <f t="shared" si="28"/>
+        <v>9075</v>
+      </c>
+      <c r="P49" s="8">
+        <f t="shared" si="28"/>
+        <v>9001</v>
+      </c>
+    </row>
+    <row r="50" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B50" t="s">
         <v>40</v>
       </c>
-      <c r="H49" s="8">
+      <c r="H50" s="8">
         <v>1325</v>
       </c>
-      <c r="I49" s="8">
+      <c r="I50" s="8">
         <v>2121</v>
       </c>
-      <c r="J49" s="8">
-        <f>1571-I49-H49</f>
+      <c r="J50" s="8">
+        <f>1571-I50-H50</f>
         <v>-1875</v>
-      </c>
-      <c r="K49" s="8"/>
-      <c r="L49" s="8"/>
-      <c r="M49" s="8">
-        <v>4965</v>
-      </c>
-      <c r="N49" s="8">
-        <v>4140</v>
-      </c>
-    </row>
-    <row r="50" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B50" t="s">
-        <v>41</v>
-      </c>
-      <c r="H50" s="8">
-        <v>2206</v>
-      </c>
-      <c r="I50" s="8">
-        <v>2381</v>
-      </c>
-      <c r="J50" s="8">
-        <f>6962-I50-H50</f>
-        <v>2375</v>
       </c>
       <c r="K50" s="8"/>
       <c r="L50" s="8"/>
       <c r="M50" s="8">
-        <v>2024</v>
+        <v>4965</v>
       </c>
       <c r="N50" s="8">
-        <v>2060</v>
-      </c>
-    </row>
-    <row r="51" spans="2:22" x14ac:dyDescent="0.25">
+        <v>4140</v>
+      </c>
+    </row>
+    <row r="51" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H51" s="8">
-        <v>139</v>
+        <v>2206</v>
       </c>
       <c r="I51" s="8">
-        <v>149</v>
+        <v>2381</v>
       </c>
       <c r="J51" s="8">
-        <f>437-I51-H51</f>
-        <v>149</v>
+        <f>6962-I51-H51</f>
+        <v>2375</v>
       </c>
       <c r="K51" s="8"/>
       <c r="L51" s="8"/>
       <c r="M51" s="8">
-        <v>142</v>
+        <v>2024</v>
       </c>
       <c r="N51" s="8">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="52" spans="2:22" x14ac:dyDescent="0.25">
+        <v>2060</v>
+      </c>
+    </row>
+    <row r="52" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H52" s="8">
-        <v>1582</v>
+        <v>139</v>
       </c>
       <c r="I52" s="8">
-        <v>1457</v>
+        <v>149</v>
       </c>
       <c r="J52" s="8">
-        <f>4427-I52-H52</f>
-        <v>1388</v>
+        <f>437-I52-H52</f>
+        <v>149</v>
       </c>
       <c r="K52" s="8"/>
       <c r="L52" s="8"/>
       <c r="M52" s="8">
-        <v>1771</v>
+        <v>142</v>
       </c>
       <c r="N52" s="8">
-        <v>2322</v>
-      </c>
-    </row>
-    <row r="53" spans="2:22" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="53" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H53" s="8">
-        <v>-294</v>
+        <v>1582</v>
       </c>
       <c r="I53" s="8">
-        <v>-511</v>
+        <v>1457</v>
       </c>
       <c r="J53" s="8">
-        <f>2833-I53-H53</f>
-        <v>3638</v>
+        <f>4427-I53-H53</f>
+        <v>1388</v>
       </c>
       <c r="K53" s="8"/>
       <c r="L53" s="8"/>
       <c r="M53" s="8">
-        <v>-571</v>
+        <v>1771</v>
       </c>
       <c r="N53" s="8">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="54" spans="2:22" x14ac:dyDescent="0.25">
+        <v>2322</v>
+      </c>
+    </row>
+    <row r="54" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H54" s="8">
-        <v>102</v>
+        <v>-294</v>
       </c>
       <c r="I54" s="8">
-        <v>119</v>
+        <v>-511</v>
       </c>
       <c r="J54" s="8">
-        <f>336-I54-H54</f>
-        <v>115</v>
+        <f>2833-I54-H54</f>
+        <v>3638</v>
       </c>
       <c r="K54" s="8"/>
       <c r="L54" s="8"/>
       <c r="M54" s="8">
-        <v>94</v>
+        <v>-571</v>
       </c>
       <c r="N54" s="8">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="55" spans="2:22" x14ac:dyDescent="0.25">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="55" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H55" s="8">
-        <v>38</v>
+        <v>102</v>
       </c>
       <c r="I55" s="8">
-        <v>92</v>
+        <v>119</v>
       </c>
       <c r="J55" s="8">
-        <f>266+105-I55-H55</f>
-        <v>241</v>
+        <f>336-I55-H55</f>
+        <v>115</v>
       </c>
       <c r="K55" s="8"/>
       <c r="L55" s="8"/>
       <c r="M55" s="8">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="N55" s="8">
-        <f>53-23</f>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="56" spans="2:22" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="56" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H56" s="8">
-        <f>1756-14-74-660-2182+891</f>
-        <v>-283</v>
+        <v>38</v>
       </c>
       <c r="I56" s="8">
-        <f>-513+82-93+251-386-569</f>
-        <v>-1228</v>
+        <v>92</v>
       </c>
       <c r="J56" s="8">
-        <f>2078+16+206-118-3913-848-I56-H56</f>
-        <v>-1068</v>
+        <f>266+105-I56-H56</f>
+        <v>241</v>
       </c>
       <c r="K56" s="8"/>
       <c r="L56" s="8"/>
       <c r="M56" s="8">
+        <v>40</v>
+      </c>
+      <c r="N56" s="8">
+        <f>53-23</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="57" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B57" t="s">
+        <v>45</v>
+      </c>
+      <c r="H57" s="8">
+        <f>1756-14-74-660-2182+891</f>
+        <v>-283</v>
+      </c>
+      <c r="I57" s="8">
+        <f>-513+82-93+251-386-569</f>
+        <v>-1228</v>
+      </c>
+      <c r="J57" s="8">
+        <f>2078+16+206-118-3913-848-I57-H57</f>
+        <v>-1068</v>
+      </c>
+      <c r="K57" s="8"/>
+      <c r="L57" s="8"/>
+      <c r="M57" s="8">
         <f>-590-109-613+287-55-830</f>
         <v>-1910</v>
       </c>
-      <c r="N56" s="8">
+      <c r="N57" s="8">
         <f>-937-163+136+511-999-442</f>
         <v>-1894</v>
       </c>
     </row>
-    <row r="57" spans="2:22" ht="13" x14ac:dyDescent="0.3">
-      <c r="B57" t="s">
+    <row r="58" spans="2:26" ht="13" x14ac:dyDescent="0.3">
+      <c r="B58" t="s">
         <v>44</v>
       </c>
-      <c r="H57" s="10">
-        <f>SUM(H49:H56)</f>
+      <c r="H58" s="10">
+        <f t="shared" ref="H58:N58" si="29">SUM(H50:H57)</f>
         <v>4815</v>
       </c>
-      <c r="I57" s="10">
-        <f>SUM(I49:I56)</f>
+      <c r="I58" s="10">
+        <f t="shared" si="29"/>
         <v>4580</v>
       </c>
-      <c r="J57" s="10">
-        <f>SUM(J49:J56)</f>
+      <c r="J58" s="10">
+        <f t="shared" si="29"/>
         <v>4963</v>
       </c>
-      <c r="K57" s="10">
-        <f>SUM(K49:K56)</f>
+      <c r="K58" s="10">
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="L57" s="10">
-        <f>SUM(L49:L56)</f>
+      <c r="L58" s="10">
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="M57" s="10">
-        <f>SUM(M49:M56)</f>
+      <c r="M58" s="10">
+        <f t="shared" si="29"/>
         <v>6555</v>
       </c>
-      <c r="N57" s="10">
-        <f>SUM(N49:N56)</f>
+      <c r="N58" s="10">
+        <f t="shared" si="29"/>
         <v>7166</v>
       </c>
-      <c r="T57" s="10">
+      <c r="X58" s="10">
         <v>13764</v>
       </c>
-      <c r="U57" s="10">
+      <c r="Y58" s="10">
         <v>16736</v>
       </c>
-      <c r="V57" s="10">
+      <c r="Z58" s="10">
         <v>18085</v>
       </c>
     </row>
-    <row r="71" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B71" t="s">
-        <v>65</v>
-      </c>
-      <c r="G71" s="3">
+    <row r="72" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B72" t="s">
+        <v>64</v>
+      </c>
+      <c r="G72" s="3">
         <v>20000</v>
       </c>
     </row>
@@ -3157,5 +3652,6 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>